--- a/knowledge_data/售前/市场与解决方案.xlsx
+++ b/knowledge_data/售前/市场与解决方案.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22905" windowHeight="12360"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -474,7 +474,7 @@
 简而言之，**myEnOS** 是 EnValt 面向家庭用户的移动端能源管理 APP，与面向 B 端的 iEnOS Web 云平台同源同后端，共同承载 EnValt “让每一度电的流动，都被精确感知、智能优化与 AI 调度”的核心理念。</t>
   </si>
   <si>
-    <t>你公司员工有几人？
+    <t>EnValt公司员工有几人？
 EnValt员工有几个？
 EnValt雇员有几个？</t>
   </si>
@@ -737,8 +737,8 @@
 - **易于安装和维护**：采用紧凑设计，便于安装和日常维护，同时支持多种通信方式，便于远程监控和管理。
 - **安全保护功能**：具备完善的故障保护功能，如直流反接保护、交流短路保护、过载保护等，确保设备和用户的安全。
 ## 应用场景
-- **三相电家用的HESS-HY-T-5~12K系列**：适用于三相电入户地区，高效能量转换、灵活配置、智能管理。
-- **工商业储能场景的HESS-HY-T-4~20K系列及CESS-HY-25~50K系列**：适用于中大型工商业用户，优化能源使用，降低运营成本。
+- **三相电家用的FX-5~12K-T系列**：适用于三相电入户地区，高效能量转换、灵活配置、智能管理。
+- **工商业储能场景的FX-25~80K-T系列**：适用于中大型工商业用户，优化能源使用，降低运营成本。
 ## 技术规格
 - **功率范围**：5kW至50kW。
 - **充放电能力**：支持高功率充电和放电，满足不同负载需求。
@@ -913,20 +913,20 @@
     <t>https://ienos.envalt-tech.com</t>
   </si>
   <si>
-    <t>质保政策</t>
+    <t>EnValt 产品的质保政策是什么？</t>
   </si>
   <si>
     <t>每种设备的质保政策不同，如果想了解详细的质保年限，请联系您的安装商。</t>
   </si>
   <si>
-    <t>怎么打开mppt阴影扫描</t>
+    <t>怎么打开mppt阴影扫描？</t>
   </si>
   <si>
     <t>阴影扫描功能在逆变器的控制项-function setting内，可控制打开或关闭。</t>
   </si>
   <si>
-    <t>小工商三相逆变器的电网侧电表
-FX-25K/30K/36K/40K/50K/80K-T逆变器的电网侧电表</t>
+    <t>如何配置小工商逆变器的电网侧电表?
+如何配置FX-25K/30K/36K/40K/50K/80K-T逆变器的电网侧电表?</t>
   </si>
   <si>
     <t># 小工商逆变器电表配置说明
@@ -943,7 +943,7 @@
 - 示例：若用户购买 **800/5A** 的 CT，则需将电表变比设置为 **160:1** 才能正常使用，且该 CT 最大可支持 **800A** 电流。
 ## 三、接线方式
 两种电表的接线方式相同，可参考以下接线图：
-[Wiring Diagram of Distribution Box（CESS series）](https://oss-cdn.hanchuess.com/Knowledge_data_base/inverter_installation_image/grid_side_line/Wiring%20Diagram%20of%20Distribution%20Box%ef%bc%88CESS%20series%ef%bc%89.pdf)
+[Wiring Diagram of Distribution Box（C&amp;I series）](https://oss-cdn.hanchuess.com/Knowledge_data_base/inverter_installation_image/grid_side_line/Wiring%20Diagram%20of%20Distribution%20Box%ef%bc%88CESS%20series%ef%bc%89.pdf)
 ## 四、技术支持
 如需选配 SM-5A 电表或了解更多信息，请联系 **EnValt 技术支持团队**。</t>
   </si>
@@ -1722,7 +1722,7 @@
 以上是充电桩的主要工作模式及其特点，希望对您有所帮助！如还有其他问题，欢迎随时咨询。</t>
   </si>
   <si>
-    <t>HESS-HY-T-5~12K逆变器如何兼容旁路光伏逆变器？</t>
+    <t>FX-5~12K-T逆变器如何兼容旁路光伏逆变器？</t>
   </si>
   <si>
     <t>### EnValt 逆变器与已有光伏逆变器的兼容解决方案
@@ -1742,7 +1742,7 @@
 如有其他疑问或需要进一步支持，欢迎随时联系我们。</t>
   </si>
   <si>
-    <t>HESS-HY-T-4~20K逆变器如何兼容旁路光伏逆变器？</t>
+    <t>FX-5~20K-T逆变器如何兼容旁路光伏逆变器？</t>
   </si>
   <si>
     <t>### EnValt FX-5K/6K/8K/10K/12K/15K/20K 逆变器与已有光伏逆变器的兼容解决方案
@@ -1761,7 +1761,7 @@
 https://oss-cdn.hanchuess.com/frontend/document/install/Three-Phase%20Inverter%20%2B%20Smart%20Meter%EF%BC%88SDM630%EF%BC%89%2B%20AC%20Coupling%20Installation%20Guide.mp4</t>
   </si>
   <si>
-    <t>CESS-HY-25~50K逆变器如何兼容旁路光伏逆变器？</t>
+    <t>FX-25~50K-T逆变器如何兼容旁路光伏逆变器？</t>
   </si>
   <si>
     <t>### FX-25K/30K/36K/40K/50K/80K-T 逆变器与现有光伏逆变器的兼容解决方案
@@ -1781,7 +1781,7 @@
 如有其他疑问或需要进一步支持，欢迎随时联系我们。</t>
   </si>
   <si>
-    <t>HESS-HY-S-3.0~6.0K逆变器如何兼容旁路光伏逆变器？
+    <t>FX-3~6K-SL逆变器如何兼容旁路光伏逆变器？
 单相逆变器电网侧如何接线？
 SDM 230电表如何接线？
 SDM 120电表如何接线？
@@ -1807,7 +1807,10 @@
 如有其他疑问或需要进一步支持，欢迎随时联系我们。</t>
   </si>
   <si>
-    <t>如何重置采集器？</t>
+    <t>如何重置采集器？
+我想重置采集器。
+怎么重置采集器？
+重置采集器怎么做？</t>
   </si>
   <si>
     <t>### 如何重置采集器
@@ -1851,7 +1854,8 @@
 希望以上信息对您有所帮助！</t>
   </si>
   <si>
-    <t>电池为什么不放电？</t>
+    <t>为什么电池不放电？
+电池不放电因为什么？</t>
   </si>
   <si>
     <t>### 为什么电池不放电？
@@ -1870,7 +1874,11 @@
 希望以上信息对您有所帮助！如有其他问题或需要进一步协助，请随时告知。</t>
   </si>
   <si>
-    <t>设备为什么无法连接到网络？</t>
+    <t>为什么设备无法连接到网络？
+设备无法连接到网络怎么办？
+我的设备无法连接到网络了。
+我的设备离线了。
+设备已离线怎么办？</t>
   </si>
   <si>
     <t>### 为什么设备无法连接到网络？
@@ -2691,7 +2699,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2756,6 +2764,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3080,7 +3091,7 @@
   <dimension ref="A1:B229"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="36.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="54.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="142.125" style="2" customWidth="1"/>
     <col min="3" max="4" width="49.125" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
@@ -3663,7 +3674,7 @@
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="19" customHeight="1" spans="1:2">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="22" t="s">
         <v>135</v>
       </c>
       <c r="B73" s="12" t="s">
@@ -3686,16 +3697,16 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" ht="25" customHeight="1" spans="1:2">
-      <c r="A76" s="11" t="s">
+    <row r="76" s="1" customFormat="1" ht="36" customHeight="1" spans="1:2">
+      <c r="A76" s="22" t="s">
         <v>141</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" ht="20" customHeight="1" spans="1:2">
-      <c r="A77" s="11" t="s">
+    <row r="77" s="1" customFormat="1" ht="111" customHeight="1" spans="1:2">
+      <c r="A77" s="22" t="s">
         <v>143</v>
       </c>
       <c r="B77" s="12" t="s">
@@ -4329,7 +4340,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B53" r:id="rId1" display="https://www.envalt-tech.com/" tooltip="https://www.envalt-tech.com/"/>
-    <hyperlink ref="B57" r:id="rId2" display="# 小工商逆变器电表配置说明&#10;&#10;适用机型：**FX-25K / 30K / 36K / 40K / 50K / 80K-T 系列**&#10;&#10;## 一、随箱标配电表：SMART METER（SM-MA）&#10;&#10;- 随箱标配 **SMART METER（SM-MA）**，包含 **MA 电表**及对应的二次侧电流为 **100mA** 的 CT。&#10;- **MA** 表示 **毫安（mA）**，即该 CT 的二次侧电流大小为 **100mA**。&#10;- 对于 **25~50K** 机型，一次侧电流为 **300A**。&#10;- 如果您的用电需求超过该阈值，可联系 **EnValt** 选配 **SM-5A 电表**。&#10;&#10;## 二、选配电表：SM-5A&#10;&#10;- **SM-5A 电表**的二次侧电流大小为 **5A**。&#10;- 该电表**不标配 CT**，需要用户自行购买二次侧电流为 **5A** 的 CT。&#10;- 电表支持调整变比进行适配，最大变比为 **1000:1**，即最大支持 **5000A** 电流。&#10;- 示例：若用户购买 **800/5A** 的 CT，则需将电表变比设置为 **160:1** 才能正常使用，且该 CT 最大可支持 **800A** 电流。&#10;&#10;## 三、接线方式&#10;&#10;两种电表的接线方式相同，可参考以下接线图：&#10;&#10;[Wiring Diagram of Distribution Box（CESS series）](https://oss-cdn.hanchuess.com/Knowledge_data_base/inverter_installation_image/grid_side_line/Wiring%20Diagram%20of%20Distribution%20Box%ef%bc%88CESS%20series%ef%bc%89.pdf)&#10;&#10;## 四、技术支持&#10;&#10;如需选配 SM-5A 电表或了解更多信息，请联系 **EnValt 技术支持团队**。" tooltip="https://oss-cdn.hanchuess.com/Knowledge_data_base/inverter_installation_image/grid_side_line/Wiring Diagram of Distribution Box%ef%bc%88CESS series%ef%bc%89.pdf"/>
+    <hyperlink ref="B57" r:id="rId2" display="# 小工商逆变器电表配置说明&#10;&#10;适用机型：**FX-25K / 30K / 36K / 40K / 50K / 80K-T 系列**&#10;&#10;## 一、随箱标配电表：SMART METER（SM-MA）&#10;&#10;- 随箱标配 **SMART METER（SM-MA）**，包含 **MA 电表**及对应的二次侧电流为 **100mA** 的 CT。&#10;- **MA** 表示 **毫安（mA）**，即该 CT 的二次侧电流大小为 **100mA**。&#10;- 对于 **25~50K** 机型，一次侧电流为 **300A**。&#10;- 如果您的用电需求超过该阈值，可联系 **EnValt** 选配 **SM-5A 电表**。&#10;&#10;## 二、选配电表：SM-5A&#10;&#10;- **SM-5A 电表**的二次侧电流大小为 **5A**。&#10;- 该电表**不标配 CT**，需要用户自行购买二次侧电流为 **5A** 的 CT。&#10;- 电表支持调整变比进行适配，最大变比为 **1000:1**，即最大支持 **5000A** 电流。&#10;- 示例：若用户购买 **800/5A** 的 CT，则需将电表变比设置为 **160:1** 才能正常使用，且该 CT 最大可支持 **800A** 电流。&#10;&#10;## 三、接线方式&#10;&#10;两种电表的接线方式相同，可参考以下接线图：&#10;&#10;[Wiring Diagram of Distribution Box（C&amp;I series）](https://oss-cdn.hanchuess.com/Knowledge_data_base/inverter_installation_image/grid_side_line/Wiring%20Diagram%20of%20Distribution%20Box%ef%bc%88CESS%20series%ef%bc%89.pdf)&#10;&#10;## 四、技术支持&#10;&#10;如需选配 SM-5A 电表或了解更多信息，请联系 **EnValt 技术支持团队**。" tooltip="https://oss-cdn.hanchuess.com/Knowledge_data_base/inverter_installation_image/grid_side_line/Wiring Diagram of Distribution Box%ef%bc%88CESS series%ef%bc%89.pdf"/>
     <hyperlink ref="B54" r:id="rId3" display="https://ienos.envalt-tech.com"/>
     <hyperlink ref="B70" r:id="rId4" display="### EnValt FX-5K/6K/8K/10K/12K/15K/20K 逆变器与已有光伏逆变器的兼容解决方案&#10;&#10;EnValt FX-5K/6K/8K/10K/12K/15K/20K 系列逆变器支持与现有光伏逆变器兼容，提供灵活的储能改造方案。具体说明如下：&#10;&#10;1. **AC 耦合安装**&#10;   - 该系列逆变器支持 AC 耦合，可与现有旁路光伏逆变器协同运行。&#10;   - 通过 AC 耦合，光伏系统产生的电力会根据 EnValt 逆变器的工作模式进行协调分配，输送至负载、电池或电网。&#10;   - 在此配置下，原有光伏逆变器可作为储能系统的一部分，优化能源使用，提升系统灵活性与可靠性。&#10;&#10;2. **智能电表集成**&#10;   - 逆变器支持与智能电表（EM-T-G1）集成，实现能源流动的实时监控与管理。&#10;   - 将智能电表接入现有光伏逆变器侧，可精确获取旁路光伏数据，确保能源高效利用。&#10;&#10;3. **安装指南**&#10;   - 安装时请确保光伏逆变器、储能逆变器、智能电表与负载之间连接正确。&#10;   - 建议参照 EnValt 提供的安装指导进行操作。&#10;&#10;具体操作流程可参考以下视频：&#10;&#10;https://oss-cdn.hanchuess.com/frontend/document/install/Three-Phase%20Inverter%20%2B%20Smart%20Meter%EF%BC%88SDM630%EF%BC%89%2B%20AC%20Coupling%20Installation%20Guide.mp4"/>
     <hyperlink ref="B71" r:id="rId4" display="### FX-25K/30K/36K/40K/50K/80K-T 逆变器与现有光伏逆变器的兼容解决方案&#10;&#10;FX-25K/30K/36K/40K/50K/80K-T 系列逆变器支持与现有光伏逆变器兼容，提供灵活的储能改造方案。具体说明如下：&#10;&#10;1. **AC 耦合安装**&#10;   - 该系列逆变器支持 AC 耦合安装，可与现有旁路光伏逆变器协同运行。&#10;   - 通过 AC 耦合，光伏系统产生的电力会根据 EnValt 逆变器的工作模式进行协调分配，输送至负载、电池或电网。&#10;   - 在此配置下，原有光伏逆变器可作为储能系统的一部分，优化能源使用，提升系统灵活性与可靠性。&#10;&#10;2. **智能电表集成**&#10;   - 逆变器支持与智能电表（EM-T-G1）集成，实现能源流动的实时监控与管理。&#10;   - 将智能电表接入现有光伏逆变器侧，可更精确地获取旁路光伏数据，确保能源高效利用。&#10;&#10;3. **安装指南**&#10;   - 安装时请确保光伏逆变器、储能逆变器、智能电表与负载之间连接正确。&#10;   - 建议参照 EnValt 提供的安装指导进行操作。&#10;&#10;具体操作流程可参考以下视频：&#10;&#10;https://oss-cdn.hanchuess.com/frontend/document/install/Three-Phase%20Inverter%20%2B%20Smart%20Meter%EF%BC%88SDM630%EF%BC%89%2B%20AC%20Coupling%20Installation%20Guide.mp4&#10;&#10;如有其他疑问或需要进一步支持，欢迎随时联系我们。"/>
